--- a/banks/W08_Kahoot匯入.xlsx
+++ b/banks/W08_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>多醣</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>單醣</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>果糖</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>醛醣</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>果糖</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>多醣</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>單醣</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -526,30 +526,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>酮醣</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>乳糖</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>蔗糖</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>雙醣</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>乳糖</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>酮醣</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>蔗糖</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -566,25 +566,25 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>蔗糖</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>多醣</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>雙醣</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>蔗糖</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -601,12 +601,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>肝醣</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>醣蛋白</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>肝醣</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -636,25 +636,25 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>果糖</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>多醣</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>酮醣</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>果糖</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>多醣</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -666,19 +666,19 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>半乳糖</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>纖維素</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>醣苷鍵</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>纖維素</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>半乳糖</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>葡萄糖</t>
@@ -689,7 +689,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -741,14 +741,14 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>肝醣</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>乳糖</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>肝醣</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>果糖</t>
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -776,25 +776,25 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>麥芽糖</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>醣蛋白</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>單醣</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>麥芽糖</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -811,17 +811,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>半乳糖</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>纖維素</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>還原糖</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>半乳糖</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -841,30 +841,30 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>醛醣</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>酮醣</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>果糖</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>澱粉</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>醛醣</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>酮醣</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>酮醣</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>乳糖</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>肝醣</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>單醣</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>乳糖</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>酮醣</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>肝醣</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>醣苷鍵</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>纖維素</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>半乳糖</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>麥芽糖</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>醣苷鍵</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>半乳糖</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>醛醣</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>肝醣</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>果糖</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>澱粉</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>果糖</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>肝醣</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>醛醣</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>單醣</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>果糖</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>酮醣</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>乳糖</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>果糖</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>酮醣</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>單醣</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>醣蛋白</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>異構物</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>醣蛋白</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>纖維素</t>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1051,30 +1051,30 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>澱粉</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>還原糖</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>澱粉</t>
-        </is>
-      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>異構物</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>醣蛋白</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>異構物</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1086,30 +1086,170 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>麥芽糖</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>纖維素</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>還原糖</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:多醣結構圖) 標號1指的是哪一種多醣?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>纖維素</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>澱粉</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>蔗糖</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>肝醣</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:多醣結構圖) 標號3指的是哪一種多醣?</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>纖維素</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>澱粉</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>麥芽糖</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>纖維素</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>葡萄糖</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>肝醣</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>澱粉—α(1→4)鏈偶爾有α(1→6)分支</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>蔗糖—由兩個葡萄糖組成</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>纖維素—動物儲存能量用的多醣</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>肝醣—人體無法消化的β鍵多醣</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>麥芽糖完全水解後可以得到幾個葡萄糖分子?</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>0個</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1個</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3個</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2個</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
